--- a/results/04_final_refined_daily_hydroclimate_data/601/Daily_temperature_and_precipitation_station_601.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Daily_temperature_and_precipitation_station_601.xlsx
@@ -679,10 +679,10 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="E8">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="F8">
         <v>17.9</v>
@@ -782,7 +782,7 @@
         <v>21.3</v>
       </c>
       <c r="K10">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="L10">
         <v>17.6</v>
@@ -808,10 +808,10 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="E11">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F11">
         <v>18.9</v>
@@ -857,6 +857,9 @@
       <c r="F12">
         <v>18.7</v>
       </c>
+      <c r="H12">
+        <v>14</v>
+      </c>
       <c r="J12">
         <v>18.5</v>
       </c>
@@ -895,12 +898,18 @@
       <c r="F13">
         <v>19.5</v>
       </c>
+      <c r="H13">
+        <v>15.1</v>
+      </c>
       <c r="I13">
         <v>24.9</v>
       </c>
       <c r="J13">
         <v>19.5</v>
       </c>
+      <c r="K13">
+        <v>13.8</v>
+      </c>
       <c r="L13">
         <v>15</v>
       </c>
@@ -928,7 +937,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="E14">
         <v>13.8</v>
@@ -936,6 +945,9 @@
       <c r="F14">
         <v>17.3</v>
       </c>
+      <c r="H14">
+        <v>15.4</v>
+      </c>
       <c r="J14">
         <v>17.6</v>
       </c>
@@ -974,6 +986,9 @@
       <c r="F15">
         <v>18.3</v>
       </c>
+      <c r="H15">
+        <v>16.2</v>
+      </c>
       <c r="I15">
         <v>21.4</v>
       </c>
@@ -1015,6 +1030,9 @@
       <c r="F16">
         <v>17.5</v>
       </c>
+      <c r="H16">
+        <v>15.5</v>
+      </c>
       <c r="I16">
         <v>20.4</v>
       </c>
@@ -1216,7 +1234,7 @@
         <v>17</v>
       </c>
       <c r="M20">
-        <v>13.8</v>
+        <v>14.8</v>
       </c>
       <c r="R20" s="2">
         <v>24611</v>
@@ -1333,13 +1351,13 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="E23">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="F23">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1448,7 +1466,7 @@
         <v>20.7</v>
       </c>
       <c r="L25">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="M25">
         <v>16.3</v>
@@ -1474,7 +1492,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="E26">
         <v>13.9</v>
@@ -1606,7 +1624,7 @@
         <v>23.7</v>
       </c>
       <c r="E29">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="F29">
         <v>18.1</v>
@@ -1621,7 +1639,7 @@
         <v>15.7</v>
       </c>
       <c r="M29">
-        <v>17</v>
+        <v>17.8</v>
       </c>
       <c r="R29" s="2">
         <v>24620</v>

--- a/results/04_final_refined_daily_hydroclimate_data/601/Daily_temperature_and_precipitation_station_601.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Daily_temperature_and_precipitation_station_601.xlsx
@@ -743,9 +743,6 @@
       <c r="L9">
         <v>14.8</v>
       </c>
-      <c r="M9">
-        <v>13.9</v>
-      </c>
       <c r="R9" s="2">
         <v>24600</v>
       </c>
@@ -782,7 +779,7 @@
         <v>21.3</v>
       </c>
       <c r="K10">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="L10">
         <v>17.6</v>
@@ -908,10 +905,10 @@
         <v>19.5</v>
       </c>
       <c r="K13">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="L13">
-        <v>15</v>
+        <v>18.1</v>
       </c>
       <c r="M13">
         <v>17.2</v>
@@ -955,7 +952,7 @@
         <v>17.6</v>
       </c>
       <c r="M14">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="R14" s="2">
         <v>24605</v>
@@ -995,11 +992,14 @@
       <c r="J15">
         <v>18.5</v>
       </c>
+      <c r="K15">
+        <v>15.2</v>
+      </c>
       <c r="L15">
-        <v>16.6</v>
+        <v>18.1</v>
       </c>
       <c r="M15">
-        <v>16.3</v>
+        <v>17</v>
       </c>
       <c r="R15" s="2">
         <v>24606</v>
@@ -1039,8 +1039,11 @@
       <c r="J16">
         <v>17.5</v>
       </c>
+      <c r="K16">
+        <v>14.6</v>
+      </c>
       <c r="L16">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="M16">
         <v>16.9</v>
@@ -1077,6 +1080,9 @@
       <c r="G17">
         <v>5.9</v>
       </c>
+      <c r="H17">
+        <v>15.1</v>
+      </c>
       <c r="I17">
         <v>21.5</v>
       </c>
@@ -1134,10 +1140,10 @@
         <v>17.9</v>
       </c>
       <c r="K18">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="L18">
-        <v>15.7</v>
+        <v>17.3</v>
       </c>
       <c r="M18">
         <v>16.5</v>
@@ -1278,7 +1284,7 @@
         <v>14.4</v>
       </c>
       <c r="L21">
-        <v>16</v>
+        <v>17.8</v>
       </c>
       <c r="M21">
         <v>17.1</v>
@@ -1371,11 +1377,14 @@
       <c r="J23">
         <v>18</v>
       </c>
+      <c r="K23">
+        <v>13</v>
+      </c>
       <c r="L23">
-        <v>13.2</v>
+        <v>16.8</v>
       </c>
       <c r="M23">
-        <v>14</v>
+        <v>15.4</v>
       </c>
       <c r="R23" s="2">
         <v>24614</v>
@@ -1419,7 +1428,7 @@
         <v>18</v>
       </c>
       <c r="L24">
-        <v>14.8</v>
+        <v>17.7</v>
       </c>
       <c r="M24">
         <v>15.8</v>
@@ -1465,11 +1474,14 @@
       <c r="J25">
         <v>20.7</v>
       </c>
+      <c r="K25">
+        <v>15.5</v>
+      </c>
       <c r="L25">
         <v>18.8</v>
       </c>
       <c r="M25">
-        <v>16.3</v>
+        <v>17.7</v>
       </c>
       <c r="R25" s="2">
         <v>24616</v>
@@ -1636,7 +1648,7 @@
         <v>23.2</v>
       </c>
       <c r="L29">
-        <v>15.7</v>
+        <v>18</v>
       </c>
       <c r="M29">
         <v>17.8</v>
@@ -1676,8 +1688,11 @@
       <c r="I30">
         <v>22</v>
       </c>
+      <c r="J30">
+        <v>18.2</v>
+      </c>
       <c r="L30">
-        <v>14</v>
+        <v>16.7</v>
       </c>
       <c r="M30">
         <v>16.8</v>
@@ -1719,9 +1734,6 @@
       </c>
       <c r="I31">
         <v>22.2</v>
-      </c>
-      <c r="K31">
-        <v>14.2</v>
       </c>
       <c r="L31">
         <v>16.5</v>
